--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>720551</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>677170</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>656250</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>656025</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>655880</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>629636</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>625000</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>620001</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>617378.5</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>613530</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>605791</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>602890.5</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>600000</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>598400</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>582410</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>576880</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>566194</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>566150</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>565030</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>564665</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>562986.5</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>560000</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>558613</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>558380</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>558167</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>542215.5</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>530930</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>520268</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>504909</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -772,9 +680,6 @@
       </c>
       <c r="B31">
         <v>500000</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>720551</v>
       </c>
+      <c r="C2">
+        <v>635706</v>
+      </c>
+      <c r="D2">
+        <v>84845</v>
+      </c>
+      <c r="E2">
+        <v>13.34657844978653</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>677170</v>
       </c>
+      <c r="C3">
+        <v>612188</v>
+      </c>
+      <c r="D3">
+        <v>64982</v>
+      </c>
+      <c r="E3">
+        <v>10.61471312733997</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>656250</v>
       </c>
+      <c r="C4">
+        <v>600000</v>
+      </c>
+      <c r="D4">
+        <v>56250</v>
+      </c>
+      <c r="E4">
+        <v>9.375</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>656025</v>
       </c>
+      <c r="C5">
+        <v>612190</v>
+      </c>
+      <c r="D5">
+        <v>43835</v>
+      </c>
+      <c r="E5">
+        <v>7.160358712164516</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>655880</v>
       </c>
+      <c r="C6">
+        <v>597270</v>
+      </c>
+      <c r="D6">
+        <v>58610</v>
+      </c>
+      <c r="E6">
+        <v>9.812982403268201</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>629636</v>
       </c>
+      <c r="C7">
+        <v>537070</v>
+      </c>
+      <c r="D7">
+        <v>92566</v>
+      </c>
+      <c r="E7">
+        <v>17.23536969110171</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>625000</v>
       </c>
+      <c r="C8">
+        <v>539375</v>
+      </c>
+      <c r="D8">
+        <v>85625</v>
+      </c>
+      <c r="E8">
+        <v>15.87485515643106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,225 +524,451 @@
       <c r="B9">
         <v>620001</v>
       </c>
+      <c r="C9">
+        <v>550000</v>
+      </c>
+      <c r="D9">
+        <v>70001</v>
+      </c>
+      <c r="E9">
+        <v>12.72745454545454</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B10">
-        <v>617378.5</v>
+        <v>619050</v>
+      </c>
+      <c r="C10">
+        <v>551809</v>
+      </c>
+      <c r="D10">
+        <v>67241</v>
+      </c>
+      <c r="E10">
+        <v>12.18555695902024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="B11">
-        <v>613530</v>
+        <v>617378.5</v>
+      </c>
+      <c r="C11">
+        <v>544270</v>
+      </c>
+      <c r="D11">
+        <v>73108.5</v>
+      </c>
+      <c r="E11">
+        <v>13.43239568596468</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="B12">
-        <v>605791</v>
+        <v>613530</v>
+      </c>
+      <c r="C12">
+        <v>557330</v>
+      </c>
+      <c r="D12">
+        <v>56200</v>
+      </c>
+      <c r="E12">
+        <v>10.08379236717922</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="B13">
-        <v>602890.5</v>
+        <v>605791</v>
+      </c>
+      <c r="C13">
+        <v>533125</v>
+      </c>
+      <c r="D13">
+        <v>72666</v>
+      </c>
+      <c r="E13">
+        <v>13.63019929660023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="B14">
-        <v>600000</v>
+        <v>602890.5</v>
+      </c>
+      <c r="C14">
+        <v>531505</v>
+      </c>
+      <c r="D14">
+        <v>71385.5</v>
+      </c>
+      <c r="E14">
+        <v>13.43082379281475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="B15">
-        <v>598400</v>
+        <v>600000</v>
+      </c>
+      <c r="C15">
+        <v>524626</v>
+      </c>
+      <c r="D15">
+        <v>75374</v>
+      </c>
+      <c r="E15">
+        <v>14.36718729151816</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="B16">
-        <v>582410</v>
+        <v>598400</v>
+      </c>
+      <c r="C16">
+        <v>534480</v>
+      </c>
+      <c r="D16">
+        <v>63920</v>
+      </c>
+      <c r="E16">
+        <v>11.95928753180662</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="B17">
-        <v>576880</v>
+        <v>582410</v>
+      </c>
+      <c r="C17">
+        <v>523617</v>
+      </c>
+      <c r="D17">
+        <v>58793</v>
+      </c>
+      <c r="E17">
+        <v>11.22824507225701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="B18">
-        <v>566194</v>
+        <v>576880</v>
+      </c>
+      <c r="C18">
+        <v>516786</v>
+      </c>
+      <c r="D18">
+        <v>60094</v>
+      </c>
+      <c r="E18">
+        <v>11.62841098636573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="B19">
-        <v>566150</v>
+        <v>566194</v>
+      </c>
+      <c r="C19">
+        <v>505800</v>
+      </c>
+      <c r="D19">
+        <v>60394</v>
+      </c>
+      <c r="E19">
+        <v>11.94029260577303</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="B20">
-        <v>565030</v>
+        <v>566150</v>
+      </c>
+      <c r="C20">
+        <v>506583</v>
+      </c>
+      <c r="D20">
+        <v>59567</v>
+      </c>
+      <c r="E20">
+        <v>11.75858645078891</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="B21">
-        <v>564665</v>
+        <v>565030</v>
+      </c>
+      <c r="C21">
+        <v>500000</v>
+      </c>
+      <c r="D21">
+        <v>65030</v>
+      </c>
+      <c r="E21">
+        <v>13.00600000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="B22">
-        <v>562986.5</v>
+        <v>564665</v>
+      </c>
+      <c r="C22">
+        <v>506250</v>
+      </c>
+      <c r="D22">
+        <v>58415</v>
+      </c>
+      <c r="E22">
+        <v>11.53876543209877</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="B23">
-        <v>560000</v>
+        <v>562986.5</v>
+      </c>
+      <c r="C23">
+        <v>502514.5</v>
+      </c>
+      <c r="D23">
+        <v>60472</v>
+      </c>
+      <c r="E23">
+        <v>12.03388160938639</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="B24">
-        <v>558613</v>
+        <v>560000</v>
+      </c>
+      <c r="C24">
+        <v>489139</v>
+      </c>
+      <c r="D24">
+        <v>70861</v>
+      </c>
+      <c r="E24">
+        <v>14.48688409634071</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="B25">
-        <v>558380</v>
+        <v>558613</v>
+      </c>
+      <c r="C25">
+        <v>489970</v>
+      </c>
+      <c r="D25">
+        <v>68643</v>
+      </c>
+      <c r="E25">
+        <v>14.0096332428516</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="B26">
-        <v>558167</v>
+        <v>558380</v>
+      </c>
+      <c r="C26">
+        <v>496013</v>
+      </c>
+      <c r="D26">
+        <v>62367</v>
+      </c>
+      <c r="E26">
+        <v>12.57366238384881</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="B27">
-        <v>542215.5</v>
+        <v>558167</v>
+      </c>
+      <c r="C27">
+        <v>498421</v>
+      </c>
+      <c r="D27">
+        <v>59746</v>
+      </c>
+      <c r="E27">
+        <v>11.98705512006917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="B28">
-        <v>530930</v>
+        <v>542215.5</v>
+      </c>
+      <c r="C28">
+        <v>481457</v>
+      </c>
+      <c r="D28">
+        <v>60758.5</v>
+      </c>
+      <c r="E28">
+        <v>12.61971474088028</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="B29">
-        <v>520268</v>
+        <v>530930</v>
+      </c>
+      <c r="C29">
+        <v>486441</v>
+      </c>
+      <c r="D29">
+        <v>44489</v>
+      </c>
+      <c r="E29">
+        <v>9.145816244930005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="B30">
-        <v>504909</v>
+        <v>520268</v>
+      </c>
+      <c r="C30">
+        <v>478000</v>
+      </c>
+      <c r="D30">
+        <v>42268</v>
+      </c>
+      <c r="E30">
+        <v>8.842677824267774</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>504909</v>
+      </c>
+      <c r="C31">
+        <v>462528</v>
+      </c>
+      <c r="D31">
+        <v>42381</v>
+      </c>
+      <c r="E31">
+        <v>9.162904732254052</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Empedrado</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>500000</v>
+      </c>
+      <c r="C32">
+        <v>421250</v>
+      </c>
+      <c r="D32">
+        <v>78750</v>
+      </c>
+      <c r="E32">
+        <v>18.69436201780415</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_maule.xlsx
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -987,310 +987,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>566194</v>
+          <t>Curepto</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chanco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>565030</v>
+          <t>Empedrado</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colbún</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>613530</v>
+          <t>Pencahue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Constitución</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>655880</v>
+          <t>Linares</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Curepto</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>605791</v>
+          <t>Longaví</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curicó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>620001</v>
+          <t>Talca</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Empedrado</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>500000</v>
+          <t>Chanco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hualañé</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>562986.5</v>
+          <t>Pelluhue</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Licantén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>656025</v>
+          <t>Constitución</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linares</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>617378.5</v>
+          <t>Licantén</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Longaví</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>558613</v>
+          <t>Vichuquén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>677170</v>
+          <t>Cauquenes</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Molina</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>576880</v>
+          <t>Río Claro</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parral</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>558167</v>
+          <t>Pelarco</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pelarco</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>600000</v>
+          <t>San Javier</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>656250</v>
+          <t>Villa Alegre</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pencahue</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>629636</v>
+          <t>Yerbas Buenas</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rauco</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>504909</v>
+          <t>Maule</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Retiro</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>542215.5</v>
+          <t>San Rafael</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Río Claro</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>520268</v>
+          <t>Sagrada Familia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Romeral</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>560000</v>
+          <t>Retiro</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>566150</v>
+          <t>Curicó</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Clemente</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>602890.5</v>
+          <t>Molina</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>San Javier</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>598400</v>
+          <t>Colbún</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Rafael</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>625000</v>
+          <t>San Clemente</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Talca</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>720551</v>
+          <t>Hualañé</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Teno</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>558380</v>
+          <t>Rauco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>530930</v>
+          <t>Teno</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>582410</v>
+          <t>Romeral</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>564665</v>
+          <t>Parral</t>
+        </is>
       </c>
     </row>
   </sheetData>
